--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8704,0.0175,0.0151,0.0713</t>
-  </si>
-  <si>
-    <t>0.8723,0.0098,0.0064,0.0669</t>
-  </si>
-  <si>
-    <t>0.6598,0.0914,0.0144,0.0610</t>
-  </si>
-  <si>
-    <t>0.8684,0.0390,0.0038,0.0178</t>
-  </si>
-  <si>
-    <t>0.8684,0.0195,0.0018,0.0285</t>
-  </si>
-  <si>
-    <t>0.8923,0.0213,0.0024,0.0162</t>
-  </si>
-  <si>
-    <t>0.7459,0.0284,0.0075,0.1123</t>
-  </si>
-  <si>
-    <t>0.8587,0.0330,0.0031,0.0234</t>
-  </si>
-  <si>
-    <t>0.8010,0.0297,0.0059,0.0489</t>
-  </si>
-  <si>
-    <t>0.5993,0.0605,0.0137,0.1350</t>
-  </si>
-  <si>
-    <t>0.9010,0.0188,0.0018,0.0162</t>
-  </si>
-  <si>
-    <t>0.7272,0.0617,0.0051,0.0345</t>
-  </si>
-  <si>
-    <t>0.7996,0.0691,0.0370,0.0407</t>
-  </si>
-  <si>
-    <t>0.8847,0.0265,0.0536,0.0140</t>
-  </si>
-  <si>
-    <t>0.9244,0.0112,0.0403,0.0148</t>
-  </si>
-  <si>
-    <t>0.7206,0.1577,0.0926,0.0314</t>
-  </si>
-  <si>
-    <t>0.8889,0.0402,0.0164,0.0183</t>
-  </si>
-  <si>
-    <t>0.5554,0.4596,0.0227,0.0052</t>
-  </si>
-  <si>
-    <t>0.1069,0.9069,0.0664,0.0031</t>
-  </si>
-  <si>
-    <t>0.5027,0.3780,0.0457,0.0227</t>
-  </si>
-  <si>
-    <t>0.5575,0.3110,0.0108,0.0140</t>
-  </si>
-  <si>
-    <t>0.3696,0.5094,0.0293,0.0188</t>
-  </si>
-  <si>
-    <t>0.9105,0.0168,0.0181,0.0238</t>
-  </si>
-  <si>
-    <t>0.8611,0.0312,0.0799,0.0247</t>
-  </si>
-  <si>
-    <t>0.9218,0.0081,0.0511,0.0095</t>
-  </si>
-  <si>
-    <t>0.7579,0.0617,0.1244,0.0476</t>
-  </si>
-  <si>
-    <t>0.7679,0.0343,0.2222,0.0198</t>
-  </si>
-  <si>
-    <t>0.9122,0.0074,0.0698,0.0091</t>
-  </si>
-  <si>
-    <t>0.1253,0.1278,0.8964,0.0050</t>
-  </si>
-  <si>
-    <t>0.7375,0.2721,0.0042,0.0034</t>
-  </si>
-  <si>
-    <t>0.9048,0.0132,0.0069,0.0320</t>
-  </si>
-  <si>
-    <t>0.1568,0.5015,0.7284,0.0204</t>
-  </si>
-  <si>
-    <t>0.5761,0.1581,0.3252,0.0128</t>
-  </si>
-  <si>
-    <t>0.7645,0.0854,0.0389,0.0526</t>
-  </si>
-  <si>
-    <t>0.8447,0.0292,0.0150,0.0603</t>
-  </si>
-  <si>
-    <t>0.3883,0.4559,0.0394,0.0201</t>
-  </si>
-  <si>
-    <t>0.6399,0.1095,0.0188,0.0630</t>
-  </si>
-  <si>
-    <t>0.0289,0.8937,0.5921,0.0098</t>
-  </si>
-  <si>
-    <t>0.6418,0.0213,0.3542,0.0144</t>
-  </si>
-  <si>
-    <t>0.5049,0.0214,0.5509,0.0064</t>
-  </si>
-  <si>
-    <t>0.9350,0.0048,0.0510,0.0071</t>
-  </si>
-  <si>
-    <t>0.9391,0.0040,0.0506,0.0044</t>
-  </si>
-  <si>
-    <t>0.0711,0.8572,0.2832,0.0301</t>
-  </si>
-  <si>
-    <t>0.8716,0.0113,0.0937,0.0125</t>
-  </si>
-  <si>
-    <t>0.7870,0.0501,0.0186,0.0521</t>
-  </si>
-  <si>
-    <t>0.2933,0.4751,0.0210,0.0369</t>
-  </si>
-  <si>
-    <t>0.4973,0.4320,0.0141,0.0090</t>
-  </si>
-  <si>
-    <t>0.4570,0.4360,0.0303,0.0143</t>
-  </si>
-  <si>
-    <t>0.1309,0.6118,0.6236,0.0153</t>
-  </si>
-  <si>
-    <t>0.0667,0.4957,0.8709,0.0039</t>
-  </si>
-  <si>
-    <t>0.8595,0.0121,0.1458,0.0076</t>
-  </si>
-  <si>
-    <t>0.5589,0.0243,0.5603,0.0077</t>
-  </si>
-  <si>
-    <t>0.0039,0.7149,0.9845,0.0002</t>
-  </si>
-  <si>
-    <t>0.6780,0.0268,0.4125,0.0037</t>
-  </si>
-  <si>
-    <t>0.8361,0.0960,0.0109,0.0116</t>
-  </si>
-  <si>
-    <t>0.8640,0.0262,0.0026,0.0184</t>
-  </si>
-  <si>
-    <t>0.6291,0.1251,0.0152,0.0353</t>
-  </si>
-  <si>
-    <t>0.3629,0.5941,0.0378,0.0126</t>
-  </si>
-  <si>
-    <t>0.7625,0.1449,0.0117,0.0142</t>
-  </si>
-  <si>
-    <t>0.7641,0.0413,0.0097,0.0671</t>
-  </si>
-  <si>
-    <t>0.9161,0.0209,0.0018,0.0103</t>
-  </si>
-  <si>
-    <t>0.0009,0.9597,0.9707,0.0004</t>
-  </si>
-  <si>
-    <t>0.0337,0.2765,0.9549,0.0031</t>
-  </si>
-  <si>
-    <t>0.6170,0.0090,0.5320,0.0030</t>
-  </si>
-  <si>
-    <t>0.1134,0.9144,0.0537,0.0031</t>
-  </si>
-  <si>
-    <t>0.0767,0.0293,0.9643,0.0003</t>
-  </si>
-  <si>
-    <t>0.4025,0.7193,0.0204,0.0017</t>
-  </si>
-  <si>
-    <t>0.0029,0.9932,0.0735,0.0011</t>
-  </si>
-  <si>
-    <t>0.8518,0.0495,0.0132,0.0221</t>
-  </si>
-  <si>
-    <t>0.5106,0.2787,0.0512,0.0515</t>
-  </si>
-  <si>
-    <t>0.2312,0.5666,0.4791,0.0086</t>
-  </si>
-  <si>
-    <t>0.0106,0.6991,0.9481,0.0013</t>
-  </si>
-  <si>
-    <t>0.3435,0.4176,0.3160,0.0084</t>
-  </si>
-  <si>
-    <t>0.0018,0.9825,0.8359,0.0010</t>
-  </si>
-  <si>
-    <t>0.0199,0.8480,0.8646,0.0072</t>
-  </si>
-  <si>
-    <t>0.7328,0.0264,0.0104,0.1271</t>
-  </si>
-  <si>
-    <t>0.8554,0.0124,0.0082,0.0784</t>
-  </si>
-  <si>
-    <t>0.6063,0.1373,0.0152,0.0724</t>
-  </si>
-  <si>
-    <t>0.7225,0.0160,0.0049,0.1875</t>
-  </si>
-  <si>
-    <t>0.8200,0.0427,0.0165,0.0624</t>
-  </si>
-  <si>
-    <t>0.7547,0.0176,0.0124,0.1881</t>
-  </si>
-  <si>
-    <t>0.0549,0.7314,0.7205,0.0023</t>
-  </si>
-  <si>
-    <t>0.0360,0.4768,0.9099,0.0029</t>
-  </si>
-  <si>
-    <t>0.5464,0.0963,0.3972,0.0297</t>
-  </si>
-  <si>
-    <t>0.3027,0.1641,0.6631,0.0096</t>
-  </si>
-  <si>
-    <t>0.0313,0.8023,0.7733,0.0069</t>
-  </si>
-  <si>
-    <t>0.2871,0.3340,0.5256,0.0102</t>
-  </si>
-  <si>
-    <t>0.8860,0.0470,0.0071,0.0117</t>
-  </si>
-  <si>
-    <t>0.8702,0.0343,0.0051,0.0193</t>
-  </si>
-  <si>
-    <t>0.8980,0.0221,0.0022,0.0151</t>
-  </si>
-  <si>
-    <t>0.8323,0.0417,0.0055,0.0221</t>
-  </si>
-  <si>
-    <t>0.6368,0.1080,0.0127,0.0386</t>
-  </si>
-  <si>
-    <t>0.4879,0.3415,0.0162,0.0191</t>
-  </si>
-  <si>
-    <t>0.5166,0.1548,0.0216,0.0644</t>
-  </si>
-  <si>
-    <t>0.6446,0.0917,0.0151,0.0689</t>
-  </si>
-  <si>
-    <t>0.9102,0.0282,0.0090,0.0191</t>
-  </si>
-  <si>
-    <t>0.7011,0.1506,0.0138,0.0161</t>
-  </si>
-  <si>
-    <t>0.7085,0.2270,0.0166,0.0095</t>
-  </si>
-  <si>
-    <t>0.7065,0.1226,0.0121,0.0238</t>
-  </si>
-  <si>
-    <t>0.8067,0.0551,0.0125,0.0413</t>
-  </si>
-  <si>
-    <t>0.8202,0.0369,0.0048,0.0332</t>
-  </si>
-  <si>
-    <t>0.6466,0.1487,0.0142,0.0323</t>
-  </si>
-  <si>
-    <t>0.6351,0.1043,0.0207,0.0703</t>
-  </si>
-  <si>
-    <t>0.1922,0.1165,0.8027,0.0191</t>
-  </si>
-  <si>
-    <t>0.2964,0.0810,0.7351,0.0134</t>
-  </si>
-  <si>
-    <t>0.9193,0.0094,0.0666,0.0088</t>
-  </si>
-  <si>
-    <t>0.8573,0.0383,0.0535,0.0204</t>
-  </si>
-  <si>
-    <t>0.0511,0.9411,0.0120,0.0044</t>
-  </si>
-  <si>
-    <t>0.4697,0.5555,0.0245,0.0091</t>
-  </si>
-  <si>
-    <t>0.3549,0.5068,0.0384,0.0284</t>
-  </si>
-  <si>
-    <t>0.1593,0.8104,0.0558,0.0079</t>
-  </si>
-  <si>
-    <t>0.3364,0.6550,0.0185,0.0079</t>
-  </si>
-  <si>
-    <t>0.0162,0.9614,0.0271,0.0089</t>
-  </si>
-  <si>
-    <t>0.2181,0.7753,0.0770,0.0094</t>
-  </si>
-  <si>
-    <t>0.9607,0.0127,0.0022,0.0049</t>
-  </si>
-  <si>
-    <t>0.7660,0.0760,0.1111,0.0253</t>
-  </si>
-  <si>
-    <t>0.8913,0.0201,0.0106,0.0317</t>
-  </si>
-  <si>
-    <t>0.9058,0.0127,0.0053,0.0346</t>
-  </si>
-  <si>
-    <t>0.5119,0.0957,0.0582,0.2499</t>
-  </si>
-  <si>
-    <t>0.7467,0.2324,0.0048,0.0040</t>
-  </si>
-  <si>
-    <t>0.6443,0.2416,0.0188,0.0195</t>
-  </si>
-  <si>
-    <t>0.5551,0.3607,0.0269,0.0120</t>
-  </si>
-  <si>
-    <t>0.0097,0.9283,0.8408,0.0060</t>
-  </si>
-  <si>
-    <t>0.6161,0.3538,0.0162,0.0054</t>
-  </si>
-  <si>
-    <t>0.5697,0.2689,0.0271,0.0273</t>
-  </si>
-  <si>
-    <t>0.6251,0.1260,0.0218,0.0536</t>
-  </si>
-  <si>
-    <t>0.8405,0.0481,0.0093,0.0215</t>
-  </si>
-  <si>
-    <t>0.4535,0.1986,0.0196,0.0748</t>
-  </si>
-  <si>
-    <t>0.7801,0.0711,0.0093,0.0290</t>
-  </si>
-  <si>
-    <t>0.6839,0.1466,0.0296,0.0309</t>
-  </si>
-  <si>
-    <t>0.8042,0.0451,0.0051,0.0270</t>
-  </si>
-  <si>
-    <t>0.7830,0.0704,0.0182,0.0463</t>
-  </si>
-  <si>
-    <t>0.8087,0.0741,0.0296,0.0426</t>
-  </si>
-  <si>
-    <t>0.7357,0.0762,0.0041,0.0263</t>
-  </si>
-  <si>
-    <t>0.3327,0.3945,0.3836,0.0036</t>
-  </si>
-  <si>
-    <t>0.3593,0.1672,0.6039,0.0082</t>
-  </si>
-  <si>
-    <t>0.4297,0.0365,0.6589,0.0032</t>
-  </si>
-  <si>
-    <t>0.7425,0.0548,0.2011,0.0064</t>
-  </si>
-  <si>
-    <t>0.9439,0.0279,0.0065,0.0025</t>
-  </si>
-  <si>
-    <t>0.8871,0.0500,0.0074,0.0104</t>
-  </si>
-  <si>
-    <t>0.9523,0.0070,0.0073,0.0128</t>
-  </si>
-  <si>
-    <t>0.8929,0.0246,0.0070,0.0287</t>
-  </si>
-  <si>
-    <t>0.6388,0.0158,0.0058,0.2962</t>
-  </si>
-  <si>
-    <t>0.8563,0.0291,0.0091,0.0547</t>
-  </si>
-  <si>
-    <t>0.7807,0.0075,0.0047,0.2136</t>
-  </si>
-  <si>
-    <t>0.8490,0.0316,0.0172,0.0487</t>
-  </si>
-  <si>
-    <t>0.1800,0.7289,0.2651,0.0176</t>
-  </si>
-  <si>
-    <t>0.8894,0.0326,0.0096,0.0207</t>
-  </si>
-  <si>
-    <t>0.7287,0.1800,0.0409,0.0223</t>
-  </si>
-  <si>
-    <t>0.8871,0.0237,0.0043,0.0268</t>
-  </si>
-  <si>
-    <t>0.7932,0.0673,0.0111,0.0362</t>
-  </si>
-  <si>
-    <t>0.9093,0.0279,0.0055,0.0133</t>
-  </si>
-  <si>
-    <t>0.9114,0.0125,0.0025,0.0260</t>
-  </si>
-  <si>
-    <t>0.8195,0.0633,0.0086,0.0190</t>
-  </si>
-  <si>
-    <t>0.0142,0.9071,0.7907,0.0106</t>
-  </si>
-  <si>
-    <t>0.9175,0.0267,0.0035,0.0090</t>
-  </si>
-  <si>
-    <t>0.9404,0.0170,0.0028,0.0073</t>
-  </si>
-  <si>
-    <t>0.5440,0.3452,0.0248,0.0150</t>
-  </si>
-  <si>
-    <t>0.8709,0.0332,0.0085,0.0181</t>
-  </si>
-  <si>
-    <t>0.7173,0.0495,0.0087,0.0671</t>
-  </si>
-  <si>
-    <t>0.6653,0.0695,0.0092,0.0641</t>
-  </si>
-  <si>
-    <t>0.8511,0.0692,0.0200,0.0150</t>
-  </si>
-  <si>
-    <t>0.7776,0.0517,0.0105,0.0502</t>
-  </si>
-  <si>
-    <t>0.7968,0.0285,0.0057,0.0527</t>
-  </si>
-  <si>
-    <t>0.7078,0.0587,0.0110,0.0833</t>
-  </si>
-  <si>
-    <t>0.8820,0.0330,0.0037,0.0187</t>
-  </si>
-  <si>
-    <t>0.8507,0.0576,0.0068,0.0151</t>
-  </si>
-  <si>
-    <t>0.8218,0.0294,0.0075,0.0539</t>
-  </si>
-  <si>
-    <t>0.7445,0.1546,0.0213,0.0165</t>
-  </si>
-  <si>
-    <t>0.9103,0.0135,0.0021,0.0169</t>
-  </si>
-  <si>
-    <t>0.7539,0.0349,0.0074,0.0774</t>
-  </si>
-  <si>
-    <t>0.5560,0.0777,0.0103,0.1054</t>
-  </si>
-  <si>
-    <t>0.8807,0.0364,0.0049,0.0124</t>
-  </si>
-  <si>
-    <t>0.5498,0.1463,0.0167,0.0551</t>
-  </si>
-  <si>
-    <t>0.7039,0.1623,0.0721,0.0658</t>
-  </si>
-  <si>
-    <t>0.8687,0.0214,0.0034,0.0279</t>
-  </si>
-  <si>
-    <t>0.6129,0.1695,0.0350,0.0537</t>
-  </si>
-  <si>
-    <t>0.8067,0.1076,0.0089,0.0124</t>
-  </si>
-  <si>
-    <t>0.8979,0.0442,0.0076,0.0113</t>
-  </si>
-  <si>
-    <t>0.0134,0.5949,0.9585,0.0020</t>
-  </si>
-  <si>
-    <t>0.8940,0.0566,0.0093,0.0091</t>
-  </si>
-  <si>
-    <t>0.0734,0.0649,0.9564,0.0009</t>
-  </si>
-  <si>
-    <t>0.6666,0.1626,0.1870,0.0089</t>
-  </si>
-  <si>
-    <t>0.1302,0.0556,0.9149,0.0018</t>
-  </si>
-  <si>
-    <t>0.1233,0.3264,0.8081,0.0081</t>
-  </si>
-  <si>
-    <t>0.6153,0.0225,0.4312,0.0096</t>
-  </si>
-  <si>
-    <t>0.1068,0.0419,0.9242,0.0029</t>
-  </si>
-  <si>
-    <t>0.7706,0.0147,0.2645,0.0106</t>
-  </si>
-  <si>
-    <t>0.7366,0.1218,0.0898,0.0252</t>
-  </si>
-  <si>
-    <t>0.8134,0.0531,0.0398,0.0564</t>
-  </si>
-  <si>
-    <t>0.8767,0.0461,0.0118,0.0198</t>
-  </si>
-  <si>
-    <t>0.8826,0.0517,0.0226,0.0084</t>
-  </si>
-  <si>
-    <t>0.6741,0.2599,0.0379,0.0156</t>
-  </si>
-  <si>
-    <t>0.9346,0.0172,0.0166,0.0050</t>
-  </si>
-  <si>
-    <t>0.8790,0.0278,0.0090,0.0318</t>
-  </si>
-  <si>
-    <t>0.7178,0.1105,0.0325,0.0435</t>
-  </si>
-  <si>
-    <t>0.2723,0.6971,0.0811,0.0129</t>
-  </si>
-  <si>
-    <t>0.8578,0.0568,0.0059,0.0130</t>
-  </si>
-  <si>
-    <t>0.5012,0.3391,0.0182,0.0235</t>
-  </si>
-  <si>
-    <t>0.7451,0.1583,0.0116,0.0156</t>
-  </si>
-  <si>
-    <t>0.8721,0.0279,0.0009,0.0082</t>
-  </si>
-  <si>
-    <t>0.9191,0.0034,0.0057,0.0497</t>
-  </si>
-  <si>
-    <t>0.8973,0.0335,0.0484,0.0109</t>
-  </si>
-  <si>
-    <t>0.9648,0.0053,0.0128,0.0043</t>
-  </si>
-  <si>
-    <t>0.9032,0.0244,0.0269,0.0097</t>
-  </si>
-  <si>
-    <t>0.8065,0.1004,0.0457,0.0126</t>
-  </si>
-  <si>
-    <t>0.2428,0.5217,0.5036,0.0261</t>
-  </si>
-  <si>
-    <t>0.3570,0.0938,0.6016,0.0209</t>
-  </si>
-  <si>
-    <t>0.9563,0.0085,0.0284,0.0020</t>
-  </si>
-  <si>
-    <t>0.7435,0.0395,0.1890,0.0340</t>
-  </si>
-  <si>
-    <t>0.3837,0.1854,0.4780,0.0483</t>
-  </si>
-  <si>
-    <t>0.9207,0.0356,0.0041,0.0059</t>
-  </si>
-  <si>
-    <t>0.8741,0.0538,0.0030,0.0081</t>
-  </si>
-  <si>
-    <t>0.7249,0.0730,0.0147,0.0522</t>
-  </si>
-  <si>
-    <t>0.7407,0.1039,0.0095,0.0248</t>
-  </si>
-  <si>
-    <t>0.6632,0.1093,0.0080,0.0420</t>
-  </si>
-  <si>
-    <t>0.7410,0.0526,0.0104,0.0593</t>
-  </si>
-  <si>
-    <t>0.8085,0.0182,0.0024,0.0569</t>
-  </si>
-  <si>
-    <t>0.4806,0.3236,0.0237,0.0284</t>
-  </si>
-  <si>
-    <t>0.8963,0.0370,0.0306,0.0140</t>
-  </si>
-  <si>
-    <t>0.4585,0.3363,0.0967,0.0882</t>
-  </si>
-  <si>
-    <t>0.6882,0.1536,0.0196,0.0237</t>
-  </si>
-  <si>
-    <t>0.1527,0.0583,0.8910,0.0017</t>
-  </si>
-  <si>
-    <t>0.0808,0.5766,0.7256,0.0535</t>
-  </si>
-  <si>
-    <t>0.6360,0.2112,0.1648,0.0231</t>
-  </si>
-  <si>
-    <t>0.0176,0.1119,0.9857,0.0003</t>
-  </si>
-  <si>
-    <t>0.7297,0.0205,0.2226,0.0405</t>
-  </si>
-  <si>
-    <t>0.1291,0.0974,0.9176,0.0011</t>
-  </si>
-  <si>
-    <t>0.2198,0.0801,0.7287,0.0161</t>
-  </si>
-  <si>
-    <t>0.8176,0.0525,0.0782,0.0354</t>
-  </si>
-  <si>
-    <t>0.9078,0.0101,0.0589,0.0159</t>
-  </si>
-  <si>
-    <t>0.8949,0.0410,0.0162,0.0093</t>
-  </si>
-  <si>
-    <t>0.9183,0.0222,0.0044,0.0110</t>
-  </si>
-  <si>
-    <t>0.9301,0.0247,0.0023,0.0069</t>
-  </si>
-  <si>
-    <t>0.8291,0.0478,0.0037,0.0192</t>
-  </si>
-  <si>
-    <t>0.7877,0.0421,0.0063,0.0450</t>
-  </si>
-  <si>
-    <t>0.8523,0.0475,0.0077,0.0190</t>
-  </si>
-  <si>
-    <t>0.8684,0.0225,0.0023,0.0193</t>
-  </si>
-  <si>
-    <t>0.8138,0.0284,0.0031,0.0311</t>
-  </si>
-  <si>
-    <t>0.8236,0.0236,0.0037,0.0558</t>
-  </si>
-  <si>
-    <t>0.8833,0.0191,0.0020,0.0230</t>
-  </si>
-  <si>
-    <t>0.5907,0.1907,0.2354,0.0078</t>
-  </si>
-  <si>
-    <t>0.0783,0.0418,0.9446,0.0011</t>
-  </si>
-  <si>
-    <t>0.1868,0.4783,0.6806,0.0122</t>
-  </si>
-  <si>
-    <t>0.9087,0.0078,0.0785,0.0095</t>
-  </si>
-  <si>
-    <t>0.8308,0.0282,0.1151,0.0188</t>
-  </si>
-  <si>
-    <t>0.9335,0.0071,0.0320,0.0128</t>
-  </si>
-  <si>
-    <t>0.4714,0.2728,0.2663,0.0504</t>
-  </si>
-  <si>
-    <t>0.8150,0.0195,0.1172,0.0348</t>
-  </si>
-  <si>
-    <t>0.9405,0.0143,0.0018,0.0079</t>
-  </si>
-  <si>
-    <t>0.8541,0.0294,0.0088,0.0374</t>
-  </si>
-  <si>
-    <t>0.8998,0.0192,0.0078,0.0278</t>
-  </si>
-  <si>
-    <t>0.6405,0.0224,0.0090,0.2795</t>
-  </si>
-  <si>
-    <t>0.8842,0.0175,0.0159,0.0350</t>
-  </si>
-  <si>
-    <t>0.8955,0.0118,0.0029,0.0329</t>
+    <t>0.9861,0.0016,0.0012,0.0060</t>
+  </si>
+  <si>
+    <t>0.0521,0.0001,0.0001,0.9922</t>
+  </si>
+  <si>
+    <t>0.9569,0.0022,0.0023,0.0341</t>
+  </si>
+  <si>
+    <t>0.2994,0.0102,0.0034,0.8397</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0034,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0008,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.6453,0.0165,0.4549,0.0023</t>
+  </si>
+  <si>
+    <t>0.3708,0.0638,0.5958,0.0028</t>
+  </si>
+  <si>
+    <t>0.4296,0.0029,0.8024,0.0004</t>
+  </si>
+  <si>
+    <t>0.3335,0.0034,0.8541,0.0008</t>
+  </si>
+  <si>
+    <t>0.9558,0.0058,0.0328,0.0035</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0033,0.9950,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0236,0.9740,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.0017,0.9934,0.0083,0.0029</t>
+  </si>
+  <si>
+    <t>0.0023,0.9936,0.0048,0.0014</t>
+  </si>
+  <si>
+    <t>0.9077,0.0277,0.0430,0.0082</t>
+  </si>
+  <si>
+    <t>0.8514,0.0022,0.1975,0.0042</t>
+  </si>
+  <si>
+    <t>0.0038,0.0015,0.9958,0.0005</t>
+  </si>
+  <si>
+    <t>0.0091,0.0046,0.9905,0.0003</t>
+  </si>
+  <si>
+    <t>0.0123,0.0036,0.9845,0.0009</t>
+  </si>
+  <si>
+    <t>0.0400,0.0045,0.9742,0.0009</t>
+  </si>
+  <si>
+    <t>0.0225,0.0019,0.9692,0.0066</t>
+  </si>
+  <si>
+    <t>0.7060,0.4163,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.6249,0.0817,0.2917,0.0030</t>
+  </si>
+  <si>
+    <t>0.0010,0.0071,0.9962,0.0026</t>
+  </si>
+  <si>
+    <t>0.0057,0.9805,0.0151,0.0001</t>
+  </si>
+  <si>
+    <t>0.9844,0.0057,0.0038,0.0010</t>
+  </si>
+  <si>
+    <t>0.0799,0.0076,0.9079,0.0143</t>
+  </si>
+  <si>
+    <t>0.8922,0.1870,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.0203,0.9608,0.2031,0.0025</t>
+  </si>
+  <si>
+    <t>0.2246,0.3142,0.3710,0.0024</t>
+  </si>
+  <si>
+    <t>0.1935,0.0009,0.8699,0.0023</t>
+  </si>
+  <si>
+    <t>0.0182,0.0484,0.9661,0.0025</t>
+  </si>
+  <si>
+    <t>0.0542,0.0031,0.9806,0.0003</t>
+  </si>
+  <si>
+    <t>0.0017,0.0890,0.9935,0.0007</t>
+  </si>
+  <si>
+    <t>0.0163,0.9568,0.0465,0.0013</t>
+  </si>
+  <si>
+    <t>0.0910,0.0093,0.9374,0.0022</t>
+  </si>
+  <si>
+    <t>0.0722,0.2939,0.0080,0.7486</t>
+  </si>
+  <si>
+    <t>0.0011,0.9944,0.0034,0.0077</t>
+  </si>
+  <si>
+    <t>0.0022,0.9881,0.0489,0.0033</t>
+  </si>
+  <si>
+    <t>0.0024,0.9927,0.0131,0.0035</t>
+  </si>
+  <si>
+    <t>0.0035,0.0173,0.9913,0.0023</t>
+  </si>
+  <si>
+    <t>0.0071,0.2262,0.9479,0.0010</t>
+  </si>
+  <si>
+    <t>0.0090,0.0043,0.9869,0.0022</t>
+  </si>
+  <si>
+    <t>0.0094,0.0011,0.9929,0.0006</t>
+  </si>
+  <si>
+    <t>0.0079,0.0039,0.9894,0.0027</t>
+  </si>
+  <si>
+    <t>0.0119,0.6334,0.8639,0.0019</t>
+  </si>
+  <si>
+    <t>0.9538,0.0658,0.0033,0.0012</t>
+  </si>
+  <si>
+    <t>0.9818,0.0029,0.0111,0.0017</t>
+  </si>
+  <si>
+    <t>0.9917,0.0015,0.0016,0.0028</t>
+  </si>
+  <si>
+    <t>0.0076,0.0082,0.9929,0.0015</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9887,0.0097,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9893,0.0124,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.8624,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0148,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.0103,0.9912,0.0042</t>
+  </si>
+  <si>
+    <t>0.0009,0.8508,0.9819,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.0011,0.9975,0.0009</t>
+  </si>
+  <si>
+    <t>0.0935,0.9294,0.0040,0.0003</t>
+  </si>
+  <si>
+    <t>0.0062,0.9937,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9068,0.0084,0.1813,0.0006</t>
+  </si>
+  <si>
+    <t>0.1558,0.0285,0.8986,0.0108</t>
+  </si>
+  <si>
+    <t>0.0004,0.0030,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9833,0.9901,0.0001</t>
+  </si>
+  <si>
+    <t>0.0154,0.7129,0.5011,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9938,0.8153,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.9406,0.9580,0.0009</t>
+  </si>
+  <si>
+    <t>0.0148,0.0012,0.0263,0.9717</t>
+  </si>
+  <si>
+    <t>0.0031,0.0062,0.0029,0.9964</t>
+  </si>
+  <si>
+    <t>0.0064,0.0032,0.0008,0.9961</t>
+  </si>
+  <si>
+    <t>0.0159,0.0007,0.0025,0.9926</t>
+  </si>
+  <si>
+    <t>0.0185,0.0001,0.0006,0.9937</t>
+  </si>
+  <si>
+    <t>0.0043,0.0013,0.0046,0.9953</t>
+  </si>
+  <si>
+    <t>0.0018,0.9437,0.7610,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.7597,0.9939,0.0001</t>
+  </si>
+  <si>
+    <t>0.0128,0.8656,0.3167,0.0013</t>
+  </si>
+  <si>
+    <t>0.0051,0.2006,0.9807,0.0012</t>
+  </si>
+  <si>
+    <t>0.0004,0.9427,0.9664,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9391,0.9401,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9924,0.0080,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9901,0.0064,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0015,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9922,0.0053,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9950,0.0010,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9917,0.0030,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9736,0.0250,0.0062,0.0005</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0009,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0021,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0008,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0012,0.9968,0.0035</t>
+  </si>
+  <si>
+    <t>0.0631,0.0045,0.9475,0.0101</t>
+  </si>
+  <si>
+    <t>0.9655,0.0043,0.0443,0.0003</t>
+  </si>
+  <si>
+    <t>0.0127,0.0020,0.9917,0.0002</t>
+  </si>
+  <si>
+    <t>0.0201,0.9802,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0075,0.9867,0.0090,0.0012</t>
+  </si>
+  <si>
+    <t>0.0112,0.9839,0.0008,0.0025</t>
+  </si>
+  <si>
+    <t>0.0189,0.9689,0.0116,0.0049</t>
+  </si>
+  <si>
+    <t>0.0303,0.9783,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.9958,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.8061,0.3257,0.0057,0.0010</t>
+  </si>
+  <si>
+    <t>0.8349,0.0176,0.1584,0.0146</t>
+  </si>
+  <si>
+    <t>0.7859,0.0052,0.2764,0.0070</t>
+  </si>
+  <si>
+    <t>0.8470,0.0265,0.1364,0.0059</t>
+  </si>
+  <si>
+    <t>0.7182,0.0244,0.3298,0.0031</t>
+  </si>
+  <si>
+    <t>0.0290,0.0271,0.0170,0.9717</t>
+  </si>
+  <si>
+    <t>0.0013,0.9952,0.0033,0.0023</t>
+  </si>
+  <si>
+    <t>0.0029,0.9890,0.0014,0.0105</t>
+  </si>
+  <si>
+    <t>0.0003,0.9969,0.0073,0.0045</t>
+  </si>
+  <si>
+    <t>0.0008,0.9612,0.9333,0.0006</t>
+  </si>
+  <si>
+    <t>0.0186,0.9841,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.3426,0.7607,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.7054,0.3973,0.0199,0.0054</t>
+  </si>
+  <si>
+    <t>0.9919,0.0035,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9931,0.0015,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0002,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9761,0.0041,0.0029,0.0110</t>
+  </si>
+  <si>
+    <t>0.9968,0.0005,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0003,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9833,0.0032,0.0073,0.0040</t>
+  </si>
+  <si>
+    <t>0.9877,0.0037,0.0051,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.6211,0.9874,0.0006</t>
+  </si>
+  <si>
+    <t>0.0043,0.1803,0.9743,0.0005</t>
+  </si>
+  <si>
+    <t>0.0066,0.0191,0.9886,0.0005</t>
+  </si>
+  <si>
+    <t>0.0229,0.0738,0.9434,0.0010</t>
+  </si>
+  <si>
+    <t>0.9802,0.0067,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.9054,0.0128,0.0958,0.0022</t>
+  </si>
+  <si>
+    <t>0.2078,0.0063,0.8942,0.0018</t>
+  </si>
+  <si>
+    <t>0.8541,0.0109,0.1918,0.0025</t>
+  </si>
+  <si>
+    <t>0.1200,0.0016,0.0020,0.9595</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.0032,0.9991</t>
+  </si>
+  <si>
+    <t>0.0028,0.0147,0.0054,0.9944</t>
+  </si>
+  <si>
+    <t>0.0074,0.0005,0.0032,0.9947</t>
+  </si>
+  <si>
+    <t>0.0033,0.7018,0.8405,0.0036</t>
+  </si>
+  <si>
+    <t>0.9938,0.0022,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0884,0.9150,0.0040,0.0088</t>
+  </si>
+  <si>
+    <t>0.9943,0.0014,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.4193,0.7378,0.0019,0.0013</t>
+  </si>
+  <si>
+    <t>0.9718,0.0054,0.0135,0.0047</t>
+  </si>
+  <si>
+    <t>0.9749,0.0024,0.0069,0.0088</t>
+  </si>
+  <si>
+    <t>0.9915,0.0018,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0948,0.9947,0.0029</t>
+  </si>
+  <si>
+    <t>0.9742,0.0017,0.0013,0.0205</t>
+  </si>
+  <si>
+    <t>0.9685,0.0047,0.0058,0.0143</t>
+  </si>
+  <si>
+    <t>0.8548,0.1677,0.0162,0.0042</t>
+  </si>
+  <si>
+    <t>0.9636,0.0104,0.0089,0.0054</t>
+  </si>
+  <si>
+    <t>0.9431,0.0297,0.0165,0.0041</t>
+  </si>
+  <si>
+    <t>0.1642,0.5781,0.2401,0.0109</t>
+  </si>
+  <si>
+    <t>0.3084,0.3710,0.3316,0.0146</t>
+  </si>
+  <si>
+    <t>0.9617,0.0211,0.0093,0.0022</t>
+  </si>
+  <si>
+    <t>0.9967,0.0002,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0004,0.0011,0.0040</t>
+  </si>
+  <si>
+    <t>0.9795,0.0053,0.0123,0.0026</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0012,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9737,0.0207,0.0058,0.0016</t>
+  </si>
+  <si>
+    <t>0.9943,0.0016,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.8738,0.1645,0.0082,0.0024</t>
+  </si>
+  <si>
+    <t>0.8066,0.2553,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9340,0.0833,0.0064,0.0004</t>
+  </si>
+  <si>
+    <t>0.8797,0.1560,0.0099,0.0035</t>
+  </si>
+  <si>
+    <t>0.9845,0.0135,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.9891,0.0070,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9958,0.0012,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9494,0.0767,0.0037,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.1075,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.8795,0.0855,0.0640,0.0085</t>
+  </si>
+  <si>
+    <t>0.0089,0.0030,0.9893,0.0023</t>
+  </si>
+  <si>
+    <t>0.0054,0.0017,0.9959,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.0006,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0068,0.0352,0.9874,0.0019</t>
+  </si>
+  <si>
+    <t>0.0100,0.0170,0.9882,0.0003</t>
+  </si>
+  <si>
+    <t>0.0084,0.0024,0.9936,0.0004</t>
+  </si>
+  <si>
+    <t>0.0079,0.0045,0.9918,0.0008</t>
+  </si>
+  <si>
+    <t>0.2753,0.0047,0.7804,0.0119</t>
+  </si>
+  <si>
+    <t>0.3108,0.0068,0.8143,0.0017</t>
+  </si>
+  <si>
+    <t>0.1255,0.0424,0.8623,0.0007</t>
+  </si>
+  <si>
+    <t>0.0567,0.0164,0.9458,0.0016</t>
+  </si>
+  <si>
+    <t>0.4570,0.0259,0.6288,0.0010</t>
+  </si>
+  <si>
+    <t>0.8533,0.0177,0.1779,0.0023</t>
+  </si>
+  <si>
+    <t>0.6358,0.0019,0.6195,0.0013</t>
+  </si>
+  <si>
+    <t>0.3713,0.0987,0.5980,0.0103</t>
+  </si>
+  <si>
+    <t>0.3897,0.7953,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.1464,0.8860,0.0059,0.0025</t>
+  </si>
+  <si>
+    <t>0.9062,0.1683,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.9804,0.0224,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9775,0.0412,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9138,0.0145,0.0661,0.0027</t>
+  </si>
+  <si>
+    <t>0.9851,0.0009,0.0164,0.0003</t>
+  </si>
+  <si>
+    <t>0.9803,0.0012,0.0134,0.0015</t>
+  </si>
+  <si>
+    <t>0.8961,0.0033,0.1515,0.0026</t>
+  </si>
+  <si>
+    <t>0.9670,0.0021,0.0200,0.0047</t>
+  </si>
+  <si>
+    <t>0.0035,0.0235,0.9852,0.0230</t>
+  </si>
+  <si>
+    <t>0.0098,0.0556,0.9739,0.0040</t>
+  </si>
+  <si>
+    <t>0.0326,0.0140,0.9684,0.0028</t>
+  </si>
+  <si>
+    <t>0.0215,0.0082,0.9773,0.0013</t>
+  </si>
+  <si>
+    <t>0.0066,0.0949,0.9694,0.0003</t>
+  </si>
+  <si>
+    <t>0.9925,0.0028,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9920,0.0022,0.0035,0.0009</t>
+  </si>
+  <si>
+    <t>0.9925,0.0035,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9892,0.0080,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0023,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9967,0.0012,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9864,0.0077,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.0232,0.1522,0.9489,0.0069</t>
+  </si>
+  <si>
+    <t>0.1265,0.3341,0.6612,0.0259</t>
+  </si>
+  <si>
+    <t>0.7243,0.0143,0.2789,0.0137</t>
+  </si>
+  <si>
+    <t>0.0089,0.0052,0.9916,0.0012</t>
+  </si>
+  <si>
+    <t>0.0011,0.0049,0.9932,0.0059</t>
+  </si>
+  <si>
+    <t>0.0179,0.0248,0.9633,0.0059</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9981,0.0015</t>
+  </si>
+  <si>
+    <t>0.0076,0.0036,0.9825,0.0041</t>
+  </si>
+  <si>
+    <t>0.0027,0.0034,0.9952,0.0019</t>
+  </si>
+  <si>
+    <t>0.0107,0.0088,0.9866,0.0016</t>
+  </si>
+  <si>
+    <t>0.1088,0.0181,0.8683,0.0163</t>
+  </si>
+  <si>
+    <t>0.8951,0.0055,0.1619,0.0018</t>
+  </si>
+  <si>
+    <t>0.8922,0.0021,0.1699,0.0014</t>
+  </si>
+  <si>
+    <t>0.9530,0.0025,0.0601,0.0013</t>
+  </si>
+  <si>
+    <t>0.9881,0.0146,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9923,0.0025,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.9939,0.0033,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0014,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0024,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9899,0.0050,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.0218,0.0064,0.9775,0.0005</t>
+  </si>
+  <si>
+    <t>0.0013,0.0038,0.9976,0.0002</t>
+  </si>
+  <si>
+    <t>0.0069,0.0870,0.9737,0.0108</t>
+  </si>
+  <si>
+    <t>0.0435,0.0334,0.9289,0.0043</t>
+  </si>
+  <si>
+    <t>0.0580,0.0022,0.9540,0.0030</t>
+  </si>
+  <si>
+    <t>0.0453,0.0223,0.9141,0.0375</t>
+  </si>
+  <si>
+    <t>0.0326,0.0092,0.9561,0.0141</t>
+  </si>
+  <si>
+    <t>0.0075,0.0119,0.9663,0.0229</t>
+  </si>
+  <si>
+    <t>0.9563,0.0011,0.0042,0.0355</t>
+  </si>
+  <si>
+    <t>0.0289,0.0142,0.0012,0.9811</t>
+  </si>
+  <si>
+    <t>0.0598,0.0008,0.0134,0.9532</t>
+  </si>
+  <si>
+    <t>0.0026,0.0001,0.0013,0.9980</t>
+  </si>
+  <si>
+    <t>0.0108,0.0004,0.0004,0.9963</t>
+  </si>
+  <si>
+    <t>0.8919,0.0034,0.0078,0.1348</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
         <v>295</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3689,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
         <v>388</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
